--- a/Excel Files/COMP_STATEMENT_CS.xlsx
+++ b/Excel Files/COMP_STATEMENT_CS.xlsx
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1002</v>
+        <v>1514.89</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>YTD_PO</t>
+          <t>YTD_REGIONAL_PO</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>465154.08</v>
+        <v>418337.08</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1002.06</v>
+        <v>1514.89</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1002.06</v>
+        <v>1514.89</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>465154.08</v>
+        <v>418337.08</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2345,11 +2345,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1002.06</v>
+        <v>1515</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>YTD_REGIONAL_PO</t>
+          <t>YTD_PO</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jviduna@cvrx.com</t>
+          <t>mbrown@cvrx.com</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FLORIDA (COLON)</t>
+          <t>PACIFIC (AUSTIN)</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23340</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="7">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10834326.8532</v>
+        <v>7179916.2565</v>
       </c>
     </row>
     <row r="21" ht="15.95" customHeight="1"/>
@@ -2478,7 +2478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2636,26 +2636,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E2" s="46" t="n">
-        <v>46027</v>
+        <v>46030</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2667,6 +2667,9 @@
           <t>2026_Q1</t>
         </is>
       </c>
+      <c r="H2" s="47" t="n">
+        <v>46029</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -2679,38 +2682,48 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Morton Plant Hospital</t>
+          <t>Providence St Vincent Medical Center</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0014u00001pyTzAAAU</t>
+          <t>0017000001PgfGiAAJ</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CRX842 029235</t>
+          <t>PDX02 028846</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>006UY00000UuflaYAB</t>
+          <t>006UY00000Txns1YAB</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Vidang Nguyen</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>003UY000008RCrhYAG</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="R2" t="n">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="S2" t="n">
-        <v>32000</v>
+        <v>35000</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
@@ -2732,26 +2745,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">
-        <v>46028</v>
+        <v>46031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2764,56 +2777,56 @@
         </is>
       </c>
       <c r="H3" s="47" t="n">
-        <v>46021</v>
+        <v>46031</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025_12</t>
+          <t>2026_01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025_Q4</t>
+          <t>2026_Q1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Adventhealth Tampa</t>
+          <t>Los Robles Hospital &amp; Medical Center</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0014u00001pyTzEAAU</t>
+          <t>0014u00001pyTyOAAU</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CRX846 029104</t>
+          <t>CRX794 026205</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>006UY00000UTwP7YAL</t>
+          <t>006UY00000N69PyYAJ</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Mohammadreza Tabesh</t>
+          <t>David Aliabadi</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0034u00002XvrkxAAB</t>
+          <t>0034u00002oXzqPAAS</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>27776.1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>27776.1</v>
+        <v>28668.5393258427</v>
       </c>
       <c r="S3" t="n">
-        <v>59776.1</v>
+        <v>63668.53932584269</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -2822,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -2841,26 +2854,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E4" s="46" t="n">
-        <v>46029</v>
+        <v>46034</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2872,6 +2885,9 @@
           <t>2026_Q1</t>
         </is>
       </c>
+      <c r="H4" s="47" t="n">
+        <v>46031</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -2884,41 +2900,51 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sarasota Memorial Health Care System</t>
+          <t>Los Robles Hospital &amp; Medical Center</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0014u00001nCHqOAAW</t>
+          <t>0014u00001pyTyOAAU</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>SMH 027377</t>
+          <t>CRX794 027778</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>006UY00000PjaNZYAZ</t>
+          <t>006UY00000QaSWhYAN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Carney Chan</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0034u00002s2sEeAAI</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>84000</v>
+        <v>28000</v>
       </c>
       <c r="R4" t="n">
-        <v>84000</v>
+        <v>28668.5393258427</v>
       </c>
       <c r="S4" t="n">
-        <v>143776.1</v>
+        <v>92337.07865168538</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -2937,26 +2963,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E5" s="46" t="n">
-        <v>46031</v>
+        <v>46036</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2968,9 +2994,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H5" s="47" t="n">
-        <v>46024</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -2983,48 +3006,38 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Adventhealth New Smyrna Beach</t>
+          <t>St Joseph Hospital Orange</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0014u00001v5DwKAAU</t>
+          <t>0014u00001pyTy3AAE</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>AHSYM 029225</t>
+          <t>CRX773 029408</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>006UY00000Uu0FNYAZ</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Surya Rao</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0034u00002ZgIOoAAN</t>
+          <t>006UY00000VM5GwYAL</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>28750.7</v>
+        <v>35000</v>
       </c>
       <c r="R5" t="n">
-        <v>28750.7</v>
+        <v>35000</v>
       </c>
       <c r="S5" t="n">
-        <v>172526.8</v>
+        <v>127337.0786516854</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
@@ -3046,26 +3059,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E6" s="46" t="n">
-        <v>46037</v>
+        <v>46045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3077,6 +3090,9 @@
           <t>2026_Q1</t>
         </is>
       </c>
+      <c r="H6" s="47" t="n">
+        <v>46034</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -3089,38 +3105,48 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Tampa General Hospital</t>
+          <t>Usc Arcadia Hospital</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0017000001PgZDEAA3</t>
+          <t>0014u00001pyTyDAAU</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TPA01 028974</t>
+          <t>CRX783 029069</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>006UY00000U9xIvYAJ</t>
+          <t>006UY00000UOkGYYA1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Michael Fong</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0034u00002XPHN0AAP</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="R6" t="n">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="S6" t="n">
-        <v>200526.8</v>
+        <v>162337.0786516854</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
@@ -3142,26 +3168,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E7" s="46" t="n">
-        <v>46038</v>
+        <v>46048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3173,9 +3199,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H7" s="47" t="n">
-        <v>46038</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -3188,32 +3211,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Uf Health Jacksonville</t>
+          <t>Ucsf Medical Center</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0010g00001jmQ7bAAE</t>
+          <t>0014u00001pyZlqAAE</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>UFJAX 029098</t>
+          <t>CVR314 029551</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>006UY00000UT9rUYAT</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Sharon Natanzon</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>003UY00000VZIQ2YAP</t>
+          <t>006UY00000VfcIoYAJ</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -3223,13 +3236,13 @@
         <v>31500</v>
       </c>
       <c r="S7" t="n">
-        <v>292277.5</v>
+        <v>225337.0786516854</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>1</v>
@@ -3251,26 +3264,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E8" s="46" t="n">
-        <v>46038</v>
+        <v>46048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3282,9 +3295,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H8" s="47" t="n">
-        <v>46030</v>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -3297,48 +3307,38 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Adventhealth Zephyrhills</t>
+          <t>Ucsf Medical Center</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0014u00001pyTz0AAE</t>
+          <t>0014u00001pyZlqAAE</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>CRX832 024831</t>
+          <t>CVR314 028890</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>006UY00000KUzKIYA1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Ramanath Rao</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0034u00002Xvq3iAAB</t>
+          <t>006UY00000U3JknYAF</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>28750.7</v>
+        <v>31500</v>
       </c>
       <c r="R8" t="n">
-        <v>28750.7</v>
+        <v>31500</v>
       </c>
       <c r="S8" t="n">
-        <v>229277.5</v>
+        <v>193837.0786516854</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
@@ -3360,26 +3360,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E9" s="46" t="n">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3403,32 +3403,32 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Uf Health Jacksonville</t>
+          <t>Loma Linda University Medical Center-Murrieta</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0010g00001jmQ7bAAE</t>
+          <t>0014u00001pydEQAAY</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>UFJAX 029372</t>
+          <t>CVR457 029621</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>006UY00000VIlQ3YAL</t>
+          <t>006UY00000VpaArYAJ</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>31500</v>
+        <v>66000</v>
       </c>
       <c r="R9" t="n">
-        <v>31500</v>
+        <v>66000</v>
       </c>
       <c r="S9" t="n">
-        <v>323777.5</v>
+        <v>291337.0786516854</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -3456,26 +3456,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E10" s="46" t="n">
-        <v>46038</v>
+        <v>46051</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3487,9 +3487,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H10" s="47" t="n">
-        <v>46038</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -3502,48 +3499,38 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Uf Health Jacksonville</t>
+          <t>Legacy Emanuel Mc</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0010g00001jmQ7bAAE</t>
+          <t>0014u00001s7myLAAQ</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>UFJAX 026212</t>
+          <t>PDX06 029602</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>006UY00000N6dcXYAR</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Brenda Murphy</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>003UY000005K52HYAS</t>
+          <t>006UY00000VnRq1YAF</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>31500</v>
+        <v>32000</v>
       </c>
       <c r="R10" t="n">
-        <v>31500</v>
+        <v>32000</v>
       </c>
       <c r="S10" t="n">
-        <v>260777.5</v>
+        <v>323337.0786516854</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
@@ -3565,26 +3552,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E11" s="46" t="n">
-        <v>46041</v>
+        <v>46052</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3596,9 +3583,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H11" s="47" t="n">
-        <v>46041</v>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -3611,48 +3595,38 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Lawnwood Regional Medical Center &amp; Heart Institute</t>
+          <t>St Joseph Hospital Orange</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0014u00001s9EqJAAU</t>
+          <t>0014u00001pyTy3AAE</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>CRX323 025923</t>
+          <t>CRX773 029676</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>006UY00000MYx0zYAD</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Rizwan Alimohammad</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0034u00002ZganwAAB</t>
+          <t>006UY00000VvRzKYAV</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="R11" t="n">
-        <v>28668.5393258427</v>
+        <v>35000</v>
       </c>
       <c r="S11" t="n">
-        <v>379734.8393258427</v>
+        <v>358337.0786516854</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
@@ -3674,26 +3648,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>zcolon@cvrx.com</t>
+          <t>raustin@cvrx.com</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zilma Colon</t>
+          <t>Renée Austin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FLORIDA (VIDUNA)</t>
+          <t>PACIFIC (BROWN)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RE_06</t>
+          <t>RE_07</t>
         </is>
       </c>
       <c r="E12" s="46" t="n">
-        <v>46041</v>
+        <v>46053</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3705,12 +3679,9 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H12" s="47" t="n">
-        <v>46035</v>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026_01</t>
+          <t>2026_02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3720,55 +3691,45 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Adventhealth Sebring</t>
+          <t>Kaweah Delta Medical Center</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0014u00001mQQ2UAAW</t>
+          <t>0014u00001s9EpwAAE</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>AHSebring 028168</t>
+          <t>CRX305 029860</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>006UY00000RvJeIYAV</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Deepti Bhandare</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0034u00002ZgAkUAAV</t>
+          <t>006UY00000WRIhZYAX</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>27288.8</v>
+        <v>60000</v>
       </c>
       <c r="R12" t="n">
-        <v>27288.8</v>
+        <v>60000</v>
       </c>
       <c r="S12" t="n">
-        <v>351066.3</v>
+        <v>418337.0786516854</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Replacement</t>
+          <t>De novo</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -3777,307 +3738,6 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>zcolon@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Zilma Colon</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>FLORIDA (VIDUNA)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>RE_06</t>
-        </is>
-      </c>
-      <c r="E13" s="46" t="n">
-        <v>46045</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Tampa General Hospital</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0017000001PgZDEAA3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>TPA01 029520</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>006UY00000Vc25NYAR</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>28000</v>
-      </c>
-      <c r="R13" t="n">
-        <v>28000</v>
-      </c>
-      <c r="S13" t="n">
-        <v>407734.8393258427</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>zcolon@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Zilma Colon</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FLORIDA (VIDUNA)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>RE_06</t>
-        </is>
-      </c>
-      <c r="E14" s="46" t="n">
-        <v>46051</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Adventhealth Orlando</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0017000001LsiQyAAJ</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>AHOrl 029650</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>006UY00000VskIXYAZ</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>28750.7</v>
-      </c>
-      <c r="R14" t="n">
-        <v>28750.7</v>
-      </c>
-      <c r="S14" t="n">
-        <v>436485.5393258427</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>zcolon@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Zilma Colon</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>FLORIDA (VIDUNA)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>RE_06</t>
-        </is>
-      </c>
-      <c r="E15" s="46" t="n">
-        <v>46052</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="H15" s="47" t="n">
-        <v>46052</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Lawnwood Regional Medical Center &amp; Heart Institute</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0014u00001s9EqJAAU</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>CRX323 029670</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>006UY00000Vu8CLYAZ</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Shakoor Arain</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0034u00002Xvvn4AAB</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>28668.5393258427</v>
-      </c>
-      <c r="S15" t="n">
-        <v>465154.0786516854</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Excel Files/COMP_STATEMENT_CS.xlsx
+++ b/Excel Files/COMP_STATEMENT_CS.xlsx
@@ -2063,7 +2063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2135,11 +2135,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1514.89</v>
+        <v>290500</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>YTD_REGIONAL_PO</t>
+          <t>SALES</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2170,11 +2170,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418337.08</v>
+        <v>1500</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>TGT_PO</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1514.89</v>
+        <v>1684.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1514.89</v>
+        <v>3184.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>418337.08</v>
+        <v>290500</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2345,11 +2345,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1515</v>
+        <v>3185</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>YTD_PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026_01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sordal@cvrx.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026_Q1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1684.5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>YTD_REGIONAL_PO</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2414,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Renée Austin</t>
+          <t>Sara Ordal</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2426,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2438,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mbrown@cvrx.com</t>
+          <t>ccastillo@cvrx.com</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2450,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PACIFIC (AUSTIN)</t>
+          <t>MOUNTAIN WEST (ORDAL)</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7179916.2565</v>
+        <v>4483811.2805</v>
       </c>
     </row>
     <row r="21" ht="15.95" customHeight="1"/>
@@ -2478,7 +2513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2636,26 +2671,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Renée Austin</t>
+          <t>Sara Ordal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PACIFIC (BROWN)</t>
+          <t>MOUNTAIN WEST (CASTILLO)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_05</t>
         </is>
       </c>
       <c r="E2" s="46" t="n">
-        <v>46030</v>
+        <v>46049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2667,9 +2702,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H2" s="47" t="n">
-        <v>46029</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -2682,55 +2714,45 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Providence St Vincent Medical Center</t>
+          <t>Abrazo Arizona Heart Hospital</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0017000001PgfGiAAJ</t>
+          <t>0014u00001mPAGbAAO</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PDX02 028846</t>
+          <t>PHO01 029348</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>006UY00000Txns1YAB</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Vidang Nguyen</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>003UY000008RCrhYAG</t>
+          <t>006UY00000VBQ3lYAH</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="R2" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="S2" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>De novo</t>
+          <t>Replacement</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -2745,26 +2767,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Renée Austin</t>
+          <t>Sara Ordal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PACIFIC (BROWN)</t>
+          <t>MOUNTAIN WEST (CASTILLO)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_05</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">
-        <v>46031</v>
+        <v>46050</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2776,9 +2798,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H3" s="47" t="n">
-        <v>46031</v>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -2791,51 +2810,41 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Los Robles Hospital &amp; Medical Center</t>
+          <t>Univ Mc Of Southern Nevada</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0014u00001pyTyOAAU</t>
+          <t>0017000001RasG1AAJ</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CRX794 026205</t>
+          <t>LAS02 029675</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>006UY00000N69PyYAJ</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>David Aliabadi</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0034u00002oXzqPAAS</t>
+          <t>006UY00000VvQC1YAN</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="R3" t="n">
-        <v>28668.5393258427</v>
+        <v>35000</v>
       </c>
       <c r="S3" t="n">
-        <v>63668.53932584269</v>
+        <v>220500</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -2854,26 +2863,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Renée Austin</t>
+          <t>Sara Ordal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PACIFIC (BROWN)</t>
+          <t>MOUNTAIN WEST (CASTILLO)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_05</t>
         </is>
       </c>
       <c r="E4" s="46" t="n">
-        <v>46034</v>
+        <v>46050</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2885,9 +2894,6 @@
           <t>2026_Q1</t>
         </is>
       </c>
-      <c r="H4" s="47" t="n">
-        <v>46031</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -2900,51 +2906,41 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Los Robles Hospital &amp; Medical Center</t>
+          <t>Honorhealth Scottsdale Shea Medical Center</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0014u00001pyTyOAAU</t>
+          <t>0017000001Sm9M2AAJ</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CRX794 027778</t>
+          <t>HSS01 029093</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>006UY00000QaSWhYAN</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Carney Chan</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0034u00002s2sEeAAI</t>
+          <t>006UY00000URtVQYA1</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>28000</v>
+        <v>157500</v>
       </c>
       <c r="R4" t="n">
-        <v>28668.5393258427</v>
+        <v>157500</v>
       </c>
       <c r="S4" t="n">
-        <v>92337.07865168538</v>
+        <v>185500</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -2963,26 +2959,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Renée Austin</t>
+          <t>Sara Ordal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PACIFIC (BROWN)</t>
+          <t>MOUNTAIN WEST (CASTILLO)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_05</t>
         </is>
       </c>
       <c r="E5" s="46" t="n">
-        <v>46036</v>
+        <v>46052</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2994,6 +2990,9 @@
           <t>2026_Q1</t>
         </is>
       </c>
+      <c r="H5" s="47" t="n">
+        <v>46052</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2026_01</t>
@@ -3006,22 +3005,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>St Joseph Hospital Orange</t>
+          <t>Univ Mc Of Southern Nevada</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0014u00001pyTy3AAE</t>
+          <t>0017000001RasG1AAJ</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CRX773 029408</t>
+          <t>LAS02 028055</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>006UY00000VM5GwYAL</t>
+          <t>006UY00000RZFpaYAH</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Arjun Gururaj</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0034u00002W97SGAAZ</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -3031,13 +3040,13 @@
         <v>35000</v>
       </c>
       <c r="S5" t="n">
-        <v>127337.0786516854</v>
+        <v>255500</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
@@ -3059,26 +3068,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>raustin@cvrx.com</t>
+          <t>sordal@cvrx.com</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Renée Austin</t>
+          <t>Sara Ordal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PACIFIC (BROWN)</t>
+          <t>MOUNTAIN WEST (CASTILLO)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RE_07</t>
+          <t>RE_05</t>
         </is>
       </c>
       <c r="E6" s="46" t="n">
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3091,7 +3100,7 @@
         </is>
       </c>
       <c r="H6" s="47" t="n">
-        <v>46034</v>
+        <v>46052</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3105,32 +3114,32 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Usc Arcadia Hospital</t>
+          <t>Univ Mc Of Southern Nevada</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0014u00001pyTyDAAU</t>
+          <t>0017000001RasG1AAJ</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CRX783 029069</t>
+          <t>LAS02 028313</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>006UY00000UOkGYYA1</t>
+          <t>006UY00000SREmkYAH</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Michael Fong</t>
+          <t>Arjun Gururaj</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0034u00002XPHN0AAP</t>
+          <t>0034u00002W97SGAAZ</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -3140,7 +3149,7 @@
         <v>35000</v>
       </c>
       <c r="S6" t="n">
-        <v>162337.0786516854</v>
+        <v>290500</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -3162,582 +3171,6 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>raustin@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Renée Austin</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PACIFIC (BROWN)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RE_07</t>
-        </is>
-      </c>
-      <c r="E7" s="46" t="n">
-        <v>46048</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Ucsf Medical Center</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0014u00001pyZlqAAE</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>CVR314 029551</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>006UY00000VfcIoYAJ</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>31500</v>
-      </c>
-      <c r="R7" t="n">
-        <v>31500</v>
-      </c>
-      <c r="S7" t="n">
-        <v>225337.0786516854</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>raustin@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Renée Austin</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PACIFIC (BROWN)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RE_07</t>
-        </is>
-      </c>
-      <c r="E8" s="46" t="n">
-        <v>46048</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Ucsf Medical Center</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0014u00001pyZlqAAE</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>CVR314 028890</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>006UY00000U3JknYAF</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>31500</v>
-      </c>
-      <c r="R8" t="n">
-        <v>31500</v>
-      </c>
-      <c r="S8" t="n">
-        <v>193837.0786516854</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>raustin@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Renée Austin</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PACIFIC (BROWN)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>RE_07</t>
-        </is>
-      </c>
-      <c r="E9" s="46" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Loma Linda University Medical Center-Murrieta</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0014u00001pydEQAAY</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>CVR457 029621</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>006UY00000VpaArYAJ</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>66000</v>
-      </c>
-      <c r="R9" t="n">
-        <v>66000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>291337.0786516854</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>raustin@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Renée Austin</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PACIFIC (BROWN)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RE_07</t>
-        </is>
-      </c>
-      <c r="E10" s="46" t="n">
-        <v>46051</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Legacy Emanuel Mc</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0014u00001s7myLAAQ</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>PDX06 029602</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>006UY00000VnRq1YAF</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>32000</v>
-      </c>
-      <c r="R10" t="n">
-        <v>32000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>323337.0786516854</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>raustin@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Renée Austin</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PACIFIC (BROWN)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RE_07</t>
-        </is>
-      </c>
-      <c r="E11" s="46" t="n">
-        <v>46052</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>St Joseph Hospital Orange</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0014u00001pyTy3AAE</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>CRX773 029676</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>006UY00000VvRzKYAV</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>35000</v>
-      </c>
-      <c r="R11" t="n">
-        <v>35000</v>
-      </c>
-      <c r="S11" t="n">
-        <v>358337.0786516854</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>raustin@cvrx.com</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Renée Austin</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PACIFIC (BROWN)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>RE_07</t>
-        </is>
-      </c>
-      <c r="E12" s="46" t="n">
-        <v>46053</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026_01</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026_02</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026_Q1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Kaweah Delta Medical Center</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0014u00001s9EpwAAE</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>CRX305 029860</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>006UY00000WRIhZYAX</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="R12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="S12" t="n">
-        <v>418337.0786516854</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>De novo</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Revenue Recognized</t>
-        </is>
-      </c>
-      <c r="AD12" t="n">
         <v>0</v>
       </c>
     </row>
